--- a/docs/lab-1/calc.xlsx
+++ b/docs/lab-1/calc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\from-desktop\учеба\6 СЕМ\6. Методы обработки изображений\ipm-lab-1\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\from-desktop\учеба\6 СЕМ\6. Методы обработки изображений\ipm-lab-1\docs\lab-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B02C61-68BD-4C0E-B0DF-83513B72DE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8226D9E8-6F0C-468C-B010-03573849992C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -450,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -485,7 +485,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -512,7 +512,22 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -532,24 +547,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -836,7 +833,7 @@
   <cols>
     <col min="1" max="1" width="53.33203125" style="8" customWidth="1"/>
     <col min="2" max="2" width="15.88671875" style="1"/>
-    <col min="3" max="5" width="15.88671875" style="21"/>
+    <col min="3" max="5" width="15.88671875" style="12"/>
     <col min="6" max="16384" width="15.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -853,7 +850,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -870,7 +867,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="23"/>
+      <c r="A3" s="28"/>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
@@ -885,22 +882,22 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="27" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="14">
-        <f>(F4-C6)/$I4</f>
+        <f t="shared" ref="C4:E5" si="0">(F4-C6)/$I4</f>
         <v>-0.54882129994845175</v>
       </c>
       <c r="D4" s="10">
-        <f>(G4-D6)/$I4</f>
+        <f t="shared" si="0"/>
         <v>0.76834981992783236</v>
       </c>
       <c r="E4" s="11">
-        <f>(H4-E6)/$I4</f>
+        <f t="shared" si="0"/>
         <v>0.32929277996907103</v>
       </c>
       <c r="F4" s="1">
@@ -921,20 +918,20 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="23"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="15">
-        <f>(F5-C7)/$I5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D5" s="16">
-        <f>(G5-D7)/$I5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E5" s="17">
-        <f>(H5-E7)/$I5</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
       <c r="F5" s="1">
@@ -955,7 +952,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -972,7 +969,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="23"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
@@ -987,7 +984,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="29" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1004,7 +1001,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25"/>
+      <c r="A9" s="30"/>
       <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
@@ -1019,7 +1016,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="26"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
@@ -1034,7 +1031,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="27" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="7"/>
@@ -1044,12 +1041,12 @@
       <c r="D11" s="10">
         <v>-100</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="7"/>
       <c r="C12" s="18">
         <v>0</v>
@@ -1057,12 +1054,12 @@
       <c r="D12" s="12">
         <v>0</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="7"/>
       <c r="C13" s="18">
         <v>2</v>
@@ -1070,12 +1067,12 @@
       <c r="D13" s="12">
         <v>2</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="7"/>
       <c r="C14" s="18">
         <v>5</v>
@@ -1083,12 +1080,12 @@
       <c r="D14" s="12">
         <v>15</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="23"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="7"/>
       <c r="C15" s="15">
         <v>10</v>
@@ -1096,7 +1093,7 @@
       <c r="D15" s="16">
         <v>100</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="23" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1114,7 +1111,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="17">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1141,11 +1138,11 @@
       <c r="B18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="24">
         <v>0.5</v>
       </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="30"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:5" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
@@ -1154,11 +1151,11 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="24">
         <v>0.5</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="30"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="26"/>
     </row>
     <row r="20" spans="1:5" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
@@ -1167,11 +1164,11 @@
       <c r="B20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="24">
         <v>200</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="30"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="8">
